--- a/src/configs/Algorithms_Hyperparameters_FS.xlsx
+++ b/src/configs/Algorithms_Hyperparameters_FS.xlsx
@@ -39,6 +39,7 @@
     <sheet name="alpha_investing" sheetId="16" r:id="rId24"/>
     <sheet name="mRMR" sheetId="14" r:id="rId25"/>
     <sheet name="GRACES" sheetId="13" r:id="rId26"/>
+    <sheet name="LASSO_Stability" sheetId="29" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">AdaBoost!$A$1:$E$2</definedName>
@@ -17802,6 +17803,60 @@
   <autoFilter ref="A1:K2" xr:uid="{00000000-0009-0000-0000-00000E000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>WIF</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_bootstrap</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>selection_threshold</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>50</v>
+      </c>
+      <c r="C2">
+        <v>0.5</v>
+      </c>
+      <c r="D2">
+        <v>0.1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>n_bootstrap=50; C=0.1; selection_threshold is not applied: the selector returns the top-K features by selection frequency</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
 </worksheet>
 </file>
 
